--- a/advanced-prompting/csv/merged_answers_new30.xlsx
+++ b/advanced-prompting/csv/merged_answers_new30.xlsx
@@ -2706,7 +2706,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>The paper does not provide specific GenBank accession numbers for the sequenced HIV isolates.</t>
@@ -4506,7 +4510,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>The paper does not provide specific GenBank accession numbers for sequenced HIV isolates.</t>
@@ -6216,7 +6224,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>The paper does not provide specific GenBank accession numbers for sequenced HIV isolates.</t>
@@ -7357,7 +7369,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>Individuals in the study did not receive any ARV drug classes before sequencing.</t>
@@ -7416,7 +7432,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>No drugs were received by individuals prior to sample sequencing.</t>
@@ -7812,7 +7832,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>The GenBank accession numbers are not mentioned in the abstract or methods sections.</t>
@@ -9617,7 +9641,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
           <t>The GenBank accession numbers for sequenced HIV isolates were not explicitly mentioned in the paper.</t>
@@ -10806,7 +10834,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr">
         <is>
           <t>No ARV drug classes were received by individuals as they were ART-naïve.</t>
@@ -10901,7 +10933,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
           <t>No drugs were received as the individuals were ART-naïve.</t>
@@ -13133,7 +13169,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr">
         <is>
           <t>GenBank accession numbers were not reported in the paper.</t>
@@ -14965,7 +15005,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
           <t>The paper does not provide GenBank accession numbers for sequenced HIV isolates.</t>
@@ -16773,7 +16817,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G149" t="inlineStr">
         <is>
           <t>The paper does not provide specific GenBank accession numbers for sequenced HIV isolates.</t>
@@ -18609,7 +18657,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G165" t="inlineStr">
         <is>
           <t>The paper did not provide GenBank accession numbers for sequenced HIV isolates.</t>
@@ -20441,7 +20493,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G181" t="inlineStr">
         <is>
           <t>Not applicable.</t>
@@ -23581,7 +23637,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G209" t="inlineStr">
         <is>
           <t>Specific drugs include 3TC, FTC, AZT, and TDF among others.</t>
@@ -25194,7 +25254,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G224" t="inlineStr">
         <is>
           <t>The study does not report any drug classes received as all individuals were ART-naive.</t>
@@ -25285,7 +25349,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G225" t="inlineStr">
         <is>
           <t>No drugs were received, as all individuals were ART-naive before sampling.</t>
@@ -25697,7 +25765,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G229" t="inlineStr">
         <is>
           <t>The paper does not specify the GenBank accession numbers for sequenced HIV isolates.</t>
@@ -26458,7 +26530,11 @@
           <t>Technical</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G236" t="inlineStr">
         <is>
           <t>The samples sequenced were HIV-1 variants from infected human peripheral blood mononuclear cells (PBMCs).</t>
@@ -26886,7 +26962,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G240" t="inlineStr">
         <is>
           <t>Individuals received integrase strand transfer inhibitors (INSTIs) among other ARV classes before sample sequencing.</t>
@@ -26989,7 +27069,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G241" t="inlineStr">
         <is>
           <t>Individuals received dolutegravir (DTG) and possibly other INSTIs before sample sequencing.</t>
@@ -27425,7 +27509,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G245" t="inlineStr">
         <is>
           <t>The paper does not specify GenBank accession numbers for the sequenced HIV isolates.</t>
@@ -28646,7 +28734,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G256" t="inlineStr">
         <is>
           <t>The individuals had not received any ARV drug classes prior to sample sequencing.</t>
@@ -28745,7 +28837,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G257" t="inlineStr">
         <is>
           <t>No drugs were received by the individuals prior to sample sequencing.</t>
@@ -29181,7 +29277,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G261" t="inlineStr">
         <is>
           <t>The accession numbers are not explicitly provided in the paper.</t>
@@ -30989,7 +31089,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr"/>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G277" t="inlineStr">
         <is>
           <t>The paper does not specify the GenBank accession numbers for sequenced HIV isolates.</t>
@@ -32226,7 +32330,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr"/>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G288" t="inlineStr">
         <is>
           <t>Individuals received integrase strand transfer inhibitors (INSTIs) prior to sample sequencing.</t>
@@ -32321,7 +32429,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr"/>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G289" t="inlineStr">
         <is>
           <t>Participants received drugs like raltegravir, dolutegravir, elvitegravir or bictegravir.</t>
@@ -32755,7 +32867,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve"> None</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -34537,7 +34649,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr"/>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G309" t="inlineStr">
         <is>
           <t>The paper does not provide the GenBank accession numbers for sequenced HIV isolates.</t>
@@ -38165,7 +38281,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F341" t="inlineStr"/>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G341" t="inlineStr">
         <is>
           <t>Not specified in the text.</t>
@@ -39873,7 +39993,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr"/>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G357" t="inlineStr">
         <is>
           <t>The paper does not provide the GenBank accession numbers for sequenced HIV isolates.</t>
@@ -42874,7 +42998,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F384" t="inlineStr"/>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G384" t="inlineStr">
         <is>
           <t>Individuals did not receive any drug classes before sample sequencing as they were ART-naive.</t>
@@ -42969,7 +43097,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F385" t="inlineStr"/>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G385" t="inlineStr">
         <is>
           <t>No drugs were received by individuals as they were ART-naive.</t>
@@ -43377,7 +43509,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F389" t="inlineStr"/>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G389" t="inlineStr">
         <is>
           <t>The GenBank accession numbers were not provided in the abstract or main text shared.</t>
@@ -44090,7 +44226,11 @@
           <t>Technical</t>
         </is>
       </c>
-      <c r="F396" t="inlineStr"/>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G396" t="inlineStr">
         <is>
           <t>The samples sequenced were potentially viral isolates from patients.</t>
@@ -44510,7 +44650,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F400" t="inlineStr"/>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G400" t="inlineStr">
         <is>
           <t>The specific drug classes received are not specified in the paper.</t>
@@ -44605,7 +44749,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F401" t="inlineStr"/>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G401" t="inlineStr">
         <is>
           <t>The specific drugs received are not detailed in the paper.</t>
@@ -45770,7 +45918,11 @@
           <t>Technical</t>
         </is>
       </c>
-      <c r="F412" t="inlineStr"/>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G412" t="inlineStr">
         <is>
           <t>HIV-1 infectious clones were sequenced.</t>
@@ -46196,7 +46348,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t xml:space="preserve"> None</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
@@ -46293,7 +46445,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F417" t="inlineStr"/>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G417" t="inlineStr">
         <is>
           <t>The paper does not list specific drugs received by individuals prior to sequencing.</t>
@@ -47998,7 +48154,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F432" t="inlineStr"/>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G432" t="inlineStr">
         <is>
           <t>No drug classes were received by the individuals, as they were ART-naive.</t>
@@ -48081,7 +48241,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F433" t="inlineStr"/>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G433" t="inlineStr">
         <is>
           <t>No drugs were received by individuals, as they were ART-naive.</t>
@@ -48485,7 +48649,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F437" t="inlineStr"/>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G437" t="inlineStr">
         <is>
           <t>The paper does not specify any GenBank accession numbers for sequenced HIV isolates.</t>
@@ -50221,7 +50389,11 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F453" t="inlineStr"/>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G453" t="inlineStr">
         <is>
           <t>The accession numbers are not stated in the text provided.</t>
@@ -53405,7 +53577,11 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F481" t="inlineStr"/>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="G481" t="inlineStr">
         <is>
           <t>The specific drugs are not listed, but high resistance was noted against nevirapine (NVP) and efavirenz (EFV).</t>

--- a/advanced-prompting/csv/merged_answers_new30.xlsx
+++ b/advanced-prompting/csv/merged_answers_new30.xlsx
@@ -2706,11 +2706,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>The paper does not provide specific GenBank accession numbers for the sequenced HIV isolates.</t>
@@ -4510,11 +4506,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>The paper does not provide specific GenBank accession numbers for sequenced HIV isolates.</t>
@@ -6224,11 +6216,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>The paper does not provide specific GenBank accession numbers for sequenced HIV isolates.</t>
@@ -7369,11 +7357,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>Individuals in the study did not receive any ARV drug classes before sequencing.</t>
@@ -7432,11 +7416,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>No drugs were received by individuals prior to sample sequencing.</t>
@@ -7832,11 +7812,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>The GenBank accession numbers are not mentioned in the abstract or methods sections.</t>
@@ -9641,11 +9617,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>The GenBank accession numbers for sequenced HIV isolates were not explicitly mentioned in the paper.</t>
@@ -10834,11 +10806,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>No ARV drug classes were received by individuals as they were ART-naïve.</t>
@@ -10933,11 +10901,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>No drugs were received as the individuals were ART-naïve.</t>
@@ -13169,11 +13133,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>GenBank accession numbers were not reported in the paper.</t>
@@ -15005,11 +14965,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
           <t>The paper does not provide GenBank accession numbers for sequenced HIV isolates.</t>
@@ -16817,11 +16773,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
           <t>The paper does not provide specific GenBank accession numbers for sequenced HIV isolates.</t>
@@ -18657,11 +18609,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
           <t>The paper did not provide GenBank accession numbers for sequenced HIV isolates.</t>
@@ -20493,11 +20441,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
           <t>Not applicable.</t>
@@ -22410,7 +22354,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0 (Review paper)</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -23637,11 +23581,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
           <t>Specific drugs include 3TC, FTC, AZT, and TDF among others.</t>
@@ -25254,11 +25194,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
           <t>The study does not report any drug classes received as all individuals were ART-naive.</t>
@@ -25349,11 +25285,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr">
         <is>
           <t>No drugs were received, as all individuals were ART-naive before sampling.</t>
@@ -25765,11 +25697,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
           <t>The paper does not specify the GenBank accession numbers for sequenced HIV isolates.</t>
@@ -26530,11 +26458,7 @@
           <t>Technical</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
           <t>The samples sequenced were HIV-1 variants from infected human peripheral blood mononuclear cells (PBMCs).</t>
@@ -26962,11 +26886,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
           <t>Individuals received integrase strand transfer inhibitors (INSTIs) among other ARV classes before sample sequencing.</t>
@@ -27069,11 +26989,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
           <t>Individuals received dolutegravir (DTG) and possibly other INSTIs before sample sequencing.</t>
@@ -27509,11 +27425,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr">
         <is>
           <t>The paper does not specify GenBank accession numbers for the sequenced HIV isolates.</t>
@@ -28734,11 +28646,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
           <t>The individuals had not received any ARV drug classes prior to sample sequencing.</t>
@@ -28837,11 +28745,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
           <t>No drugs were received by the individuals prior to sample sequencing.</t>
@@ -29277,11 +29181,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr">
         <is>
           <t>The accession numbers are not explicitly provided in the paper.</t>
@@ -31089,11 +30989,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
           <t>The paper does not specify the GenBank accession numbers for sequenced HIV isolates.</t>
@@ -32330,11 +32226,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F288" t="inlineStr"/>
       <c r="G288" t="inlineStr">
         <is>
           <t>Individuals received integrase strand transfer inhibitors (INSTIs) prior to sample sequencing.</t>
@@ -32429,11 +32321,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F289" t="inlineStr"/>
       <c r="G289" t="inlineStr">
         <is>
           <t>Participants received drugs like raltegravir, dolutegravir, elvitegravir or bictegravir.</t>
@@ -32867,7 +32755,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t xml:space="preserve"> None</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -34649,11 +34537,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr">
         <is>
           <t>The paper does not provide the GenBank accession numbers for sequenced HIV isolates.</t>
@@ -38281,11 +38165,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F341" t="inlineStr"/>
       <c r="G341" t="inlineStr">
         <is>
           <t>Not specified in the text.</t>
@@ -39993,11 +39873,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F357" t="inlineStr"/>
       <c r="G357" t="inlineStr">
         <is>
           <t>The paper does not provide the GenBank accession numbers for sequenced HIV isolates.</t>
@@ -42998,11 +42874,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr">
         <is>
           <t>Individuals did not receive any drug classes before sample sequencing as they were ART-naive.</t>
@@ -43097,11 +42969,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr">
         <is>
           <t>No drugs were received by individuals as they were ART-naive.</t>
@@ -43509,11 +43377,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F389" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr">
         <is>
           <t>The GenBank accession numbers were not provided in the abstract or main text shared.</t>
@@ -44226,11 +44090,7 @@
           <t>Technical</t>
         </is>
       </c>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F396" t="inlineStr"/>
       <c r="G396" t="inlineStr">
         <is>
           <t>The samples sequenced were potentially viral isolates from patients.</t>
@@ -44650,11 +44510,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F400" t="inlineStr"/>
       <c r="G400" t="inlineStr">
         <is>
           <t>The specific drug classes received are not specified in the paper.</t>
@@ -44749,11 +44605,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F401" t="inlineStr"/>
       <c r="G401" t="inlineStr">
         <is>
           <t>The specific drugs received are not detailed in the paper.</t>
@@ -45918,11 +45770,7 @@
           <t>Technical</t>
         </is>
       </c>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F412" t="inlineStr"/>
       <c r="G412" t="inlineStr">
         <is>
           <t>HIV-1 infectious clones were sequenced.</t>
@@ -46348,7 +46196,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t xml:space="preserve"> None</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
@@ -46445,11 +46293,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F417" t="inlineStr"/>
       <c r="G417" t="inlineStr">
         <is>
           <t>The paper does not list specific drugs received by individuals prior to sequencing.</t>
@@ -48154,11 +47998,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F432" t="inlineStr"/>
       <c r="G432" t="inlineStr">
         <is>
           <t>No drug classes were received by the individuals, as they were ART-naive.</t>
@@ -48241,11 +48081,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr">
         <is>
           <t>No drugs were received by individuals, as they were ART-naive.</t>
@@ -48649,11 +48485,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F437" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr">
         <is>
           <t>The paper does not specify any GenBank accession numbers for sequenced HIV isolates.</t>
@@ -50389,11 +50221,7 @@
           <t>Data availability</t>
         </is>
       </c>
-      <c r="F453" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F453" t="inlineStr"/>
       <c r="G453" t="inlineStr">
         <is>
           <t>The accession numbers are not stated in the text provided.</t>
@@ -52330,7 +52158,7 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0 (Review paper)</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
@@ -53577,11 +53405,7 @@
           <t>Treatment</t>
         </is>
       </c>
-      <c r="F481" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
+      <c r="F481" t="inlineStr"/>
       <c r="G481" t="inlineStr">
         <is>
           <t>The specific drugs are not listed, but high resistance was noted against nevirapine (NVP) and efavirenz (EFV).</t>

--- a/advanced-prompting/csv/merged_answers_new30.xlsx
+++ b/advanced-prompting/csv/merged_answers_new30.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes"""</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Sanger sequencing"""</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Plasma, DBS</t>
+          <t>Plasma, DBS"""</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes"""</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No"""</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes"""</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>NRTIs, INSTIs</t>
+          <t>Not reported"""</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>DTG, tenofovir, lamivudine, dolutegravir</t>
+          <t>Not reported"""</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No"""</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes"""</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>PV008448-PV008641, PV407014-PV407203, and PV419497-PV419583</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>227"""</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Cameroon, Côte d'Ivoire, Malawi, Republic of Congo, Uganda, Zambia, and Zimbabwe</t>
+          <t>Cameroon, Cote d'Ivoire, Malawi, Republic of Congo, Uganda, Zambia, Zimbabwe"""</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2022-2024</t>
+          <t>2022-2024"""</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No"""</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>IN, PR, RT</t>
+          <t>IN, PR, RT"""</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Tenofovir disoproxil maleate, emtricitabine</t>
+          <t>Tenofovir disoproxil fumarate/emtricitabine</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Not reported</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Plasma, Serum, PBMC</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs, INSTIs</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>Zidovudine, Didanosine, Abacavir, Tenofovir, Lopinavir, Atazanavir, Darunavir, Raltegravir, Dolutegravir, Elvitegravir, Bictegravir, Rilpivirine, Doravirine</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Not reported</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>1994-2024</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1677</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8710,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>Sanger sequencing.</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>Plasma.</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9226,7 +9226,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>NNRTI, PI.</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>EFV, NVP, ATV/r, LPV/r.</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9743,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10125,7 +10125,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>Kenya.</t>
+          <t>Kenya</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>2011-2021.</t>
+          <t>2011-2021</t>
         </is>
       </c>
     </row>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>Not reported.</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>PR, RT.</t>
+          <t>PR, RT</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -10885,7 +10885,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>Plasma or serum</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -11007,7 +11007,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>South Korea, Asia, and the Americas</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>2021-2024</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -12353,7 +12353,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>env, gag, pol, protease, reverse transcriptase, and integrase</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -12983,7 +12983,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>ZDV, 3TC, NVP, lopinavir/ritonavir, EFV</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -14641,7 +14641,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>"Yes""""</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>"NGS""""</t>
         </is>
       </c>
     </row>
@@ -14901,7 +14901,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>"Plasma""""</t>
         </is>
       </c>
     </row>
@@ -15031,7 +15031,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>"Yes""""</t>
         </is>
       </c>
     </row>
@@ -15161,7 +15161,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>"No""""</t>
         </is>
       </c>
     </row>
@@ -15291,7 +15291,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>"Yes""""</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>NNRTIs</t>
+          <t>"NNRTIs, NRTIs""""</t>
         </is>
       </c>
     </row>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>Efavirenz (EFV), Nevirapine (NVP), Lamivudine (3TC)</t>
+          <t>"Not reported"</t>
         </is>
       </c>
     </row>
@@ -15681,7 +15681,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>"No""""</t>
         </is>
       </c>
     </row>
@@ -15811,7 +15811,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>"No""""</t>
         </is>
       </c>
     </row>
@@ -16071,7 +16071,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>"20""""</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>"Ghana""""</t>
         </is>
       </c>
     </row>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>"Not reported""""</t>
         </is>
       </c>
     </row>
@@ -16461,7 +16461,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>"No""""</t>
         </is>
       </c>
     </row>
@@ -16591,7 +16591,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>"PR, RT""""</t>
         </is>
       </c>
     </row>
@@ -16851,7 +16851,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>Sanger sequencing and Next generation sequencing</t>
+          <t>Sanger sequencing, NGS</t>
         </is>
       </c>
     </row>
@@ -16973,7 +16973,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>Plasma and DBS</t>
+          <t>Plasma, DBS</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>INSTIs</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -17615,7 +17615,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>DTG, TDF, 3TC</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -18513,7 +18513,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>Whole blood</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -19159,7 +19159,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>NRTIs, INSTIs, NNRTIs, PIs</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -19809,7 +19809,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -20199,7 +20199,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -20719,7 +20719,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -20849,7 +20849,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>**Yes**</t>
         </is>
       </c>
     </row>
@@ -20979,7 +20979,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>**Sanger sequencing**</t>
         </is>
       </c>
     </row>
@@ -21109,7 +21109,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>**Plasma**</t>
         </is>
       </c>
     </row>
@@ -21239,7 +21239,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>**Yes**</t>
         </is>
       </c>
     </row>
@@ -21369,7 +21369,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>**No**</t>
         </is>
       </c>
     </row>
@@ -21499,7 +21499,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>**Yes**</t>
         </is>
       </c>
     </row>
@@ -21889,7 +21889,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>**No**</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>**No**</t>
         </is>
       </c>
     </row>
@@ -22145,7 +22145,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>**Not reported**</t>
         </is>
       </c>
     </row>
@@ -22275,7 +22275,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>**212**</t>
         </is>
       </c>
     </row>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>**Malawi**</t>
         </is>
       </c>
     </row>
@@ -22535,7 +22535,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>2022-2023</t>
+          <t>**2022-2023**</t>
         </is>
       </c>
     </row>
@@ -22665,7 +22665,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>**No**</t>
         </is>
       </c>
     </row>
@@ -22795,7 +22795,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>**PR, RT, IN**</t>
         </is>
       </c>
     </row>
@@ -23181,7 +23181,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -23567,7 +23567,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>INSTIs, NRTIs, NNRTIs</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -23827,7 +23827,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>Dolutegravir, emtricitabine, tenofovir disoproxil fumarate, bictegravir, emtricitabine, tenofovir alafenamide</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -23957,7 +23957,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24339,7 +24339,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -24981,7 +24981,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>**Yes**</t>
         </is>
       </c>
     </row>
@@ -25107,7 +25107,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>**Not reported**</t>
         </is>
       </c>
     </row>
@@ -25233,7 +25233,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>**Not reported**</t>
         </is>
       </c>
     </row>
@@ -25359,7 +25359,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>**Yes**</t>
         </is>
       </c>
     </row>
@@ -25485,7 +25485,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>**No**</t>
         </is>
       </c>
     </row>
@@ -25611,7 +25611,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>**Yes**</t>
         </is>
       </c>
     </row>
@@ -25737,7 +25737,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs, INSTIs</t>
+          <t>**Not reported**</t>
         </is>
       </c>
     </row>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>3TC, FTC, AZT, TDF, EFV, NVP, DTG</t>
+          <t>**Not reported**</t>
         </is>
       </c>
     </row>
@@ -25993,7 +25993,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>**No**</t>
         </is>
       </c>
     </row>
@@ -26119,7 +26119,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>**No**</t>
         </is>
       </c>
     </row>
@@ -26245,7 +26245,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>**Not reported**</t>
         </is>
       </c>
     </row>
@@ -26371,7 +26371,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>**9685**</t>
         </is>
       </c>
     </row>
@@ -26501,7 +26501,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>**Tanzania**</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>2004-2024</t>
+          <t>**Not reported**</t>
         </is>
       </c>
     </row>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>**Not reported**</t>
         </is>
       </c>
     </row>
@@ -26883,7 +26883,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>RT, PR</t>
+          <t>**Not reported**</t>
         </is>
       </c>
     </row>
@@ -27005,7 +27005,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -27123,7 +27123,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>Sanger sequencing.</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -27245,7 +27245,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>Plasma.</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -27367,7 +27367,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27489,7 +27489,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27615,7 +27615,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27729,7 +27729,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27843,7 +27843,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27965,7 +27965,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28091,7 +28091,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>1,159.00</t>
+          <t>1048</t>
         </is>
       </c>
     </row>
@@ -28461,7 +28461,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>China.</t>
+          <t>China</t>
         </is>
       </c>
     </row>
@@ -28587,7 +28587,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>2019-2022.</t>
+          <t>2019-2022</t>
         </is>
       </c>
     </row>
@@ -28709,7 +28709,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>PR, RT.</t>
+          <t>PR, RT</t>
         </is>
       </c>
     </row>
@@ -29201,7 +29201,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -29323,7 +29323,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -29445,7 +29445,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -29567,7 +29567,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -30795,7 +30795,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>Gag-Pol, Env-Nef</t>
+          <t>Env, NC, IN</t>
         </is>
       </c>
     </row>
@@ -31181,7 +31181,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -31429,7 +31429,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -31925,7 +31925,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -32055,7 +32055,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -32307,7 +32307,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -32681,7 +32681,7 @@
       </c>
       <c r="Z256" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -32811,7 +32811,7 @@
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>gag, protease</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -32937,7 +32937,7 @@
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -33063,7 +33063,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>Not reported (but likely Sanger sequencing or NGS).</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -33193,7 +33193,7 @@
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>Whole blood.</t>
+          <t>Whole blood</t>
         </is>
       </c>
     </row>
@@ -33319,7 +33319,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33445,7 +33445,7 @@
       </c>
       <c r="Z262" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -33571,7 +33571,7 @@
       </c>
       <c r="Z263" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -33701,7 +33701,7 @@
       </c>
       <c r="Z264" t="inlineStr">
         <is>
-          <t>Not reported.</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -33827,7 +33827,7 @@
       </c>
       <c r="Z265" t="inlineStr">
         <is>
-          <t>Not reported.</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -33953,7 +33953,7 @@
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34083,7 +34083,7 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>Not reported.</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34339,7 +34339,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -34469,7 +34469,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>Not reported.</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -34599,7 +34599,7 @@
       </c>
       <c r="Z271" t="inlineStr">
         <is>
-          <t>1997-2019.</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -34725,7 +34725,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>Not reported.</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34855,7 +34855,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>PR, RT, IN.</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -35241,7 +35241,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -35485,7 +35485,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35855,7 +35855,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -36245,7 +36245,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Not reported</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -36375,7 +36375,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1106</t>
         </is>
       </c>
     </row>
@@ -36765,7 +36765,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -36891,7 +36891,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>All HIV genes (PR, RT, IN, Pol, CA, Env)</t>
+          <t>All genes</t>
         </is>
       </c>
     </row>
@@ -37017,7 +37017,7 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -37395,7 +37395,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -37643,7 +37643,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -38399,7 +38399,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>249</t>
         </is>
       </c>
     </row>
@@ -38525,7 +38525,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
@@ -39033,7 +39033,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>"Yes"</t>
         </is>
       </c>
     </row>
@@ -39163,7 +39163,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>"Sanger sequencing"</t>
         </is>
       </c>
     </row>
@@ -39293,7 +39293,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>"Plasma"</t>
         </is>
       </c>
     </row>
@@ -39423,7 +39423,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>"Yes"</t>
         </is>
       </c>
     </row>
@@ -39553,7 +39553,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>"No"</t>
         </is>
       </c>
     </row>
@@ -39683,7 +39683,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>"Yes"</t>
         </is>
       </c>
     </row>
@@ -39813,7 +39813,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>INSTIs</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -39943,7 +39943,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -40073,7 +40073,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>"No"</t>
         </is>
       </c>
     </row>
@@ -40203,7 +40203,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>"No"</t>
         </is>
       </c>
     </row>
@@ -40333,7 +40333,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>"Not reported"</t>
         </is>
       </c>
     </row>
@@ -40455,7 +40455,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>"28"</t>
         </is>
       </c>
     </row>
@@ -40585,7 +40585,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>"Mozambique"</t>
         </is>
       </c>
     </row>
@@ -40711,7 +40711,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>"2022-2024"</t>
         </is>
       </c>
     </row>
@@ -40841,7 +40841,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>"No"</t>
         </is>
       </c>
     </row>
@@ -40971,7 +40971,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>"IN"</t>
         </is>
       </c>
     </row>
@@ -41609,7 +41609,7 @@
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -41865,7 +41865,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -41995,7 +41995,7 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
-          <t>ABC, 3TC, EFV, NVP, TDF, AZT, DTG, ATV, LPV</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -42121,7 +42121,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -42893,7 +42893,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -43511,7 +43511,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -43637,7 +43637,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -43763,7 +43763,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -44109,7 +44109,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -44239,7 +44239,7 @@
       </c>
       <c r="Z347" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -44483,7 +44483,7 @@
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -44605,7 +44605,7 @@
       </c>
       <c r="Z350" t="inlineStr">
         <is>
-          <t>USA, Dominican Republic</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -44727,7 +44727,7 @@
       </c>
       <c r="Z351" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -44971,7 +44971,7 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>CA (capsid)</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -45101,7 +45101,7 @@
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>"Yes"</t>
         </is>
       </c>
     </row>
@@ -45227,7 +45227,7 @@
       </c>
       <c r="Z355" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>"Not reported"</t>
         </is>
       </c>
     </row>
@@ -45353,7 +45353,7 @@
       </c>
       <c r="Z356" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>"Not reported"</t>
         </is>
       </c>
     </row>
@@ -45479,7 +45479,7 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>"Yes"</t>
         </is>
       </c>
     </row>
@@ -45609,7 +45609,7 @@
       </c>
       <c r="Z358" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>"No"</t>
         </is>
       </c>
     </row>
@@ -45735,7 +45735,7 @@
       </c>
       <c r="Z359" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>"Yes"</t>
         </is>
       </c>
     </row>
@@ -45861,7 +45861,7 @@
       </c>
       <c r="Z360" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs</t>
+          <t>"Not reported"</t>
         </is>
       </c>
     </row>
@@ -45987,7 +45987,7 @@
       </c>
       <c r="Z361" t="inlineStr">
         <is>
-          <t>AZT, TDF, NNRTIs</t>
+          <t>"Not reported"</t>
         </is>
       </c>
     </row>
@@ -46117,7 +46117,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>"No"</t>
         </is>
       </c>
     </row>
@@ -46247,7 +46247,7 @@
       </c>
       <c r="Z363" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>"No"</t>
         </is>
       </c>
     </row>
@@ -46373,7 +46373,7 @@
       </c>
       <c r="Z364" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>"Not reported"</t>
         </is>
       </c>
     </row>
@@ -46503,7 +46503,7 @@
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>"235"</t>
         </is>
       </c>
     </row>
@@ -46629,7 +46629,7 @@
       </c>
       <c r="Z366" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>"Uganda"</t>
         </is>
       </c>
     </row>
@@ -46755,7 +46755,7 @@
       </c>
       <c r="Z367" t="inlineStr">
         <is>
-          <t>2018-2023</t>
+          <t>"2018-2023"</t>
         </is>
       </c>
     </row>
@@ -46881,7 +46881,7 @@
       </c>
       <c r="Z368" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>"Not reported"</t>
         </is>
       </c>
     </row>
@@ -47007,7 +47007,7 @@
       </c>
       <c r="Z369" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>"Not reported"</t>
         </is>
       </c>
     </row>
@@ -47385,7 +47385,7 @@
       </c>
       <c r="Z372" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Plasma, Whole blood</t>
         </is>
       </c>
     </row>
@@ -48369,7 +48369,7 @@
       </c>
       <c r="Z380" t="inlineStr">
         <is>
-          <t>PV187006</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -48999,7 +48999,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>Pol, Env</t>
+          <t>Full genome</t>
         </is>
       </c>
     </row>
@@ -49121,7 +49121,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -50077,7 +50077,7 @@
       </c>
       <c r="Z394" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -50199,7 +50199,7 @@
       </c>
       <c r="Z395" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -50903,7 +50903,7 @@
       </c>
       <c r="Z401" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -51269,7 +51269,7 @@
       </c>
       <c r="Z404" t="inlineStr">
         <is>
-          <t>Infectious clones</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -51391,7 +51391,7 @@
       </c>
       <c r="Z405" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -51635,7 +51635,7 @@
       </c>
       <c r="Z407" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -51993,7 +51993,7 @@
       </c>
       <c r="Z410" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -52119,7 +52119,7 @@
       </c>
       <c r="Z411" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -52245,7 +52245,7 @@
       </c>
       <c r="Z412" t="inlineStr">
         <is>
-          <t>PQ735970-PQ735985</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -52359,7 +52359,7 @@
       </c>
       <c r="Z413" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -52485,7 +52485,7 @@
       </c>
       <c r="Z414" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -52607,7 +52607,7 @@
       </c>
       <c r="Z415" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -52729,7 +52729,7 @@
       </c>
       <c r="Z416" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -52851,7 +52851,7 @@
       </c>
       <c r="Z417" t="inlineStr">
         <is>
-          <t>Pol</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -53241,7 +53241,7 @@
       </c>
       <c r="Z420" t="inlineStr">
         <is>
-          <t>DBS and venous blood</t>
+          <t>DBS, Plasma</t>
         </is>
       </c>
     </row>
@@ -54753,7 +54753,7 @@
       </c>
       <c r="Z432" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -55005,7 +55005,7 @@
       </c>
       <c r="Z434" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -55127,7 +55127,7 @@
       </c>
       <c r="Z435" t="inlineStr">
         <is>
-          <t>Sanger sequencing.</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
     </row>
@@ -55249,7 +55249,7 @@
       </c>
       <c r="Z436" t="inlineStr">
         <is>
-          <t>Plasma.</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -55371,7 +55371,7 @@
       </c>
       <c r="Z437" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -55493,7 +55493,7 @@
       </c>
       <c r="Z438" t="inlineStr">
         <is>
-          <t>Not reported.</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -55615,7 +55615,7 @@
       </c>
       <c r="Z439" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -55741,7 +55741,7 @@
       </c>
       <c r="Z440" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs, and INSTIs.</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -55867,7 +55867,7 @@
       </c>
       <c r="Z441" t="inlineStr">
         <is>
-          <t>DTG, ABC, AZT, TDF, LPV, and EFV.</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -55989,7 +55989,7 @@
       </c>
       <c r="Z442" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -56111,7 +56111,7 @@
       </c>
       <c r="Z443" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -56473,7 +56473,7 @@
       </c>
       <c r="Z446" t="inlineStr">
         <is>
-          <t>Uganda.</t>
+          <t>Uganda</t>
         </is>
       </c>
     </row>
@@ -56717,7 +56717,7 @@
       </c>
       <c r="Z448" t="inlineStr">
         <is>
-          <t>Not reported.</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -56835,7 +56835,7 @@
       </c>
       <c r="Z449" t="inlineStr">
         <is>
-          <t>PR, RT, and possibly others.</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
     </row>
@@ -57095,7 +57095,7 @@
       </c>
       <c r="Z451" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -57225,7 +57225,7 @@
       </c>
       <c r="Z452" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -57355,7 +57355,7 @@
       </c>
       <c r="Z453" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -57485,7 +57485,7 @@
       </c>
       <c r="Z454" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -57611,7 +57611,7 @@
       </c>
       <c r="Z455" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -57741,7 +57741,7 @@
       </c>
       <c r="Z456" t="inlineStr">
         <is>
-          <t>NRTIs, capsid inhibitors</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -57871,7 +57871,7 @@
       </c>
       <c r="Z457" t="inlineStr">
         <is>
-          <t>lenacapavir, emtricitabine/tenofovir alafenamide, emtricitabine/tenofovir disoproxil fumarate</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -58387,7 +58387,7 @@
       </c>
       <c r="Z461" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>77</t>
         </is>
       </c>
     </row>
@@ -58903,7 +58903,7 @@
       </c>
       <c r="Z465" t="inlineStr">
         <is>
-          <t>CA, PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -60061,7 +60061,7 @@
       </c>
       <c r="Z474" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -60191,7 +60191,7 @@
       </c>
       <c r="Z475" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -60577,7 +60577,7 @@
       </c>
       <c r="Z478" t="inlineStr">
         <is>
-          <t>Kenya, Uganda, Tanzania, and Ethiopia</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -60707,7 +60707,7 @@
       </c>
       <c r="Z479" t="inlineStr">
         <is>
-          <t>2015-2025</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
@@ -60963,7 +60963,7 @@
       </c>
       <c r="Z481" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>

--- a/advanced-prompting/csv/merged_answers_new30.xlsx
+++ b/advanced-prompting/csv/merged_answers_new30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,60 +521,70 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>llama_8B_R8</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>llama3.1-8B R16</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>llama3.1-8B R32</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Llama3.1-70B base</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Llama3.1-70B FT-50</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Llama3.1-70B FT-100</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Llama3.1-70B FT-150</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Llama3.1-70B FT-200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Llama3.1-70B FT</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Llama3.1-70B QSP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Llama3.1-70B FT+QSP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>llama_70B_R8</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>llama3.1-70B R16</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>llama3.1-70B R32</t>
         </is>
